--- a/backend/data/clinic_data.xlsx
+++ b/backend/data/clinic_data.xlsx
@@ -16,6 +16,9 @@
     <sheet name="Staff" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="AuditLog" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Metadata" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MedicalCheckups" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Treatments" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="PatientRequests" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,18 +439,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,15 +490,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>allergies</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>medical_conditions</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>consent_status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
@@ -505,73 +532,560 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rohan dedhia</t>
+          <t>naman chauhan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9322132827</t>
+          <t>9222222222</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>acknowledged</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-05T20:56:49.996135</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-05T20:56:49.996135</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>checkup_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>patient_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>appointment_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dentist_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>blood_pressure</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>medical_conditions</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>allergies</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>oral_hygiene_habits</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>teeth_findings_json</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>canker_sores</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>canker_sores_notes</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>anomalous_teeth</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>anomalous_teeth_notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>other_oral_notes</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>consent_status</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>refusal_reason</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>treatment_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>default_duration_minutes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>request_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>patient_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>patient_phone</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>patient_age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>patient_id</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dentist_id</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>preferred_date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>preferred_start_time</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>preferred_end_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>review_notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>appointment_id</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-000001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>naman chauhan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9222222222</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PAT-000001</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DOC-000001</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>acknowledged</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-05T19:16:53.850218</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T19:16:53.850218</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Dental Extraction</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>simulator</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-09-05T20:56:50.428206</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-09-05T20:56:50.428206</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAT-000002</t>
+          <t>REQ-000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dhruv gay</t>
+          <t>naman chauhan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9222222222</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>93222 83104</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PAT-000001</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DOC-000001</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>acknowledged</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-05T19:33:02.705757</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T19:33:02.705757</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Dental Consultation</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>simulator</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-09-05T20:57:35.307747</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-09-05T20:57:35.307747</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-000003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>naman chauhan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9222222222</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PAT-000001</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DOC-000002</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dental Consultation</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>simulator</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-09-05T20:58:08.219775</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-09-05T20:58:08.219775</t>
         </is>
       </c>
     </row>
@@ -745,7 +1259,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-05T19:09:37.597257</t>
+          <t>2026-09-05T20:44:40.355075</t>
         </is>
       </c>
     </row>
@@ -787,7 +1301,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-05T19:09:37.597294</t>
+          <t>2026-09-05T20:44:40.355100</t>
         </is>
       </c>
     </row>
@@ -1494,20 +2008,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1543,141 +2062,52 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>treatment_name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>payment_status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bill_number</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>clinical_notes</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>APT-000001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>PAT-000001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DOC-000001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>cleaning</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Created via Patient WhatsApp Bot Simulator</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-09-05T19:16:54.280760</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-09-05T19:16:54.280760</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>APT-000002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PAT-000002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DOC-000001</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>cleaning</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Created via Patient WhatsApp Bot Simulator</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-09-05T19:33:03.154078</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-09-05T19:33:03.154078</t>
         </is>
       </c>
     </row>
@@ -1752,10 +2182,10 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="85" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1803,7 +2233,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05T19:16:53.850218</t>
+          <t>2026-09-05T20:56:49.996135</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1828,7 +2258,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Registered patient rohan dedhia (9322132827)</t>
+          <t>Registered patient naman chauhan (9222222222)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +2270,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-05T19:16:54.280760</t>
+          <t>2026-09-05T20:56:50.428206</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>staff_reception</t>
+          <t>simulator_bot</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>APPOINTMENT</t>
+          <t>PATIENT_REQUEST</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>APT-000001</t>
+          <t>REQ-000001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1865,7 +2295,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Booked for patient PAT-000001 with dentist DOC-000001 on 2026-09-09 (11:00-11:30)</t>
+          <t>Patient request submitted from simulator for naman chauhan</t>
         </is>
       </c>
     </row>
@@ -1877,22 +2307,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05T19:33:02.705757</t>
+          <t>2026-09-05T20:57:35.307747</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>staff_reception</t>
+          <t>simulator_bot</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PATIENT</t>
+          <t>PATIENT_REQUEST</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PAT-000002</t>
+          <t>REQ-000002</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1902,7 +2332,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Registered patient dhruv gay (93222 83104)</t>
+          <t>Patient request submitted from simulator for naman chauhan</t>
         </is>
       </c>
     </row>
@@ -1914,22 +2344,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-05T19:33:03.154078</t>
+          <t>2026-09-05T20:58:08.219775</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>staff_reception</t>
+          <t>simulator_bot</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>APPOINTMENT</t>
+          <t>PATIENT_REQUEST</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APT-000002</t>
+          <t>REQ-000003</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1939,7 +2369,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Booked for patient PAT-000002 with dentist DOC-000001 on 2026-09-07 (10:30-11:00)</t>
+          <t>Patient request submitted from simulator for naman chauhan</t>
         </is>
       </c>
     </row>
@@ -1992,7 +2422,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-05T19:09:37.597332</t>
+          <t>2026-09-05T20:44:40.355123</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2439,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-05T19:09:37.597334</t>
+          <t>2026-09-05T20:44:40.355125</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2456,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-05T19:09:37.597336</t>
+          <t>2026-09-05T20:44:40.355126</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2473,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-05T19:09:37.597338</t>
+          <t>2026-09-05T20:44:40.355127</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2490,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-05T19:09:37.597339</t>
+          <t>2026-09-05T20:44:40.355128</t>
         </is>
       </c>
     </row>

--- a/backend/data/clinic_data.xlsx
+++ b/backend/data/clinic_data.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -564,6 +564,92 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>2026-09-05T20:56:49.996135</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PAT-000002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>acknowledged</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:07:25.170585</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:07:25.170585</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PAT-000003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>naman</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1234567</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>acknowledged</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:11.292406</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:27.822949</t>
         </is>
       </c>
     </row>
@@ -764,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,13 +862,14 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -833,35 +920,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>booking_time</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>review_notes</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>appointment_id</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
@@ -913,29 +1005,30 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Dental Extraction</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>simulator</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>2026-09-05T20:56:50.428206</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2026-09-05T20:56:50.428206</t>
         </is>
@@ -987,29 +1080,30 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Dental Consultation</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>simulator</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-09-05T20:57:35.307747</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-09-05T20:57:35.307747</t>
         </is>
@@ -1061,31 +1155,498 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Dental Consultation</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>simulator</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>2026-09-05T20:58:08.219775</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>2026-09-05T20:58:08.219775</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PAT-000002</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DOC-000002</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>General Checkup</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>simulator</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:07:25.685927</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:07:25.685927</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PAT-000002</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DOC-000001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Dental Consultation</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>simulator</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:07:46.846710</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:07:46.846710</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>naman</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1234567</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PAT-000002</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DOC-000002</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:11.761151</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>General Checkup</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>simulator</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:11.761151</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:11.761151</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REQ-000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>naman</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1234567</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PAT-000002</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DOC-000002</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:36.511224</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Dental Consultation</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>simulator</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:36.511224</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:36.511224</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REQ-000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>naman</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1234567</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PAT-000002</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DOC-000001</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:49.931709</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Dental Consultation</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>simulator</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:49.931709</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:49.931709</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REQ-000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>naman</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1234567</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PAT-000002</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DOC-000002</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:40:30.142552</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Dental Consultation</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>simulator</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:40:30.142552</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:40:30.142552</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2017,16 +2578,17 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2062,50 +2624,55 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>booking_time</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>treatment_name</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>payment_status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>bill_number</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>clinical_notes</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
@@ -2176,7 +2743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2370,6 +2937,302 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>Patient request submitted from simulator for naman chauhan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LOG-000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:07:25.170585</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>staff_reception</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PATIENT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PAT-000002</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Registered patient dd (123456789)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LOG-000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:07:25.685927</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>simulator_bot</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PATIENT_REQUEST</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>REQ-000004</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Patient request submitted from simulator for dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LOG-000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:07:46.846710</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>simulator_bot</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PATIENT_REQUEST</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>REQ-000005</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Patient request submitted from simulator for dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LOG-000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:11.292406</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>staff_reception</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PATIENT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PAT-000003</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Registered patient naman (1234567)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LOG-000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:11.761151</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>simulator_bot</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PATIENT_REQUEST</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>REQ-000006</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Patient request submitted from simulator for naman</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LOG-000010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:36.511224</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>simulator_bot</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PATIENT_REQUEST</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>REQ-000007</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Patient request submitted from simulator for naman</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LOG-000011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:39:49.931709</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>simulator_bot</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PATIENT_REQUEST</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>REQ-000008</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Patient request submitted from simulator for naman</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LOG-000012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:40:30.142552</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>simulator_bot</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PATIENT_REQUEST</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>REQ-000009</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Patient request submitted from simulator for naman</t>
         </is>
       </c>
     </row>
